--- a/3x3practice.xlsx
+++ b/3x3practice.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Maths\Slot-Math-Engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83FCADE-42E1-4E84-883F-F1D49E6824B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63D7DE4-65A4-44A9-A484-33AD5A367866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseGame" sheetId="1" r:id="rId1"/>
     <sheet name="FreeGame" sheetId="2" r:id="rId2"/>
+    <sheet name="Reels" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="20">
   <si>
     <t>Reel 1</t>
   </si>
@@ -51,34 +52,31 @@
     <t>Reel 5</t>
   </si>
   <si>
-    <t>HH</t>
-  </si>
-  <si>
-    <t>EE</t>
-  </si>
-  <si>
-    <t>DD</t>
-  </si>
-  <si>
     <t>GG</t>
   </si>
   <si>
     <t>CC</t>
   </si>
   <si>
-    <t>WW</t>
+    <t>HH</t>
   </si>
   <si>
     <t>FF</t>
   </si>
   <si>
+    <t>DD</t>
+  </si>
+  <si>
     <t>AA</t>
   </si>
   <si>
-    <t>BB</t>
+    <t>WW</t>
   </si>
   <si>
-    <t>SS</t>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>BB</t>
   </si>
   <si>
     <t>Reel1</t>
@@ -94,6 +92,9 @@
   </si>
   <si>
     <t>Reel5</t>
+  </si>
+  <si>
+    <t>SS</t>
   </si>
 </sst>
 </file>
@@ -461,573 +462,573 @@
     </row>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>16</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>17</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <f>COUNTIF(A1:A100,H4)</f>
+        <f t="shared" ref="I4:I13" si="0">COUNTIF(A1:A100,H4)</f>
         <v>2</v>
       </c>
       <c r="J4">
-        <f>COUNTIF(B1:B100,H4)</f>
+        <f t="shared" ref="J4:J13" si="1">COUNTIF(B1:B100,H4)</f>
         <v>2</v>
       </c>
       <c r="K4">
-        <f>COUNTIF(C1:C100,H4)</f>
+        <f t="shared" ref="K4:K13" si="2">COUNTIF(C1:C100,H4)</f>
         <v>3</v>
       </c>
       <c r="L4">
-        <f>COUNTIF(D1:D100,H4)</f>
+        <f t="shared" ref="L4:L13" si="3">COUNTIF(D1:D100,H4)</f>
         <v>2</v>
       </c>
       <c r="M4">
-        <f>COUNTIF(E1:E100,H4)</f>
+        <f t="shared" ref="M4:M13" si="4">COUNTIF(E1:E100,H4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5">
-        <f>COUNTIF(A2:A101,H5)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J13" si="0">COUNTIF(B2:B101,H5)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K13" si="1">COUNTIF(C2:C101,H5)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L13" si="2">COUNTIF(D2:D101,H5)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="M5">
-        <f t="shared" ref="M5:M13" si="3">COUNTIF(E2:E101,H5)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I13" si="4">COUNTIF(A3:A102,H6)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="J6">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K6">
+      <c r="J12">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="M6">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7">
+      <c r="M12">
         <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="J7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
       <c r="J13">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K13">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L13">
+      <c r="K13">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M13">
+      <c r="L13">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
+      <c r="M13">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <f>SUM(I4:I13)</f>
         <v>47</v>
       </c>
       <c r="J14">
-        <f t="shared" ref="J14:M14" si="5">SUM(J4:J13)</f>
+        <f>SUM(J4:J13)</f>
         <v>45</v>
       </c>
       <c r="K14">
-        <f t="shared" si="5"/>
+        <f>SUM(K4:K13)</f>
         <v>37</v>
       </c>
       <c r="L14">
-        <f t="shared" si="5"/>
+        <f>SUM(L4:L13)</f>
         <v>46</v>
       </c>
       <c r="M14">
-        <f t="shared" si="5"/>
+        <f>SUM(M4:M13)</f>
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1035,13 +1036,13 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
@@ -1049,47 +1050,47 @@
     </row>
     <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -1100,70 +1101,70 @@
     </row>
     <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1171,369 +1172,369 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1542,7 +1543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C92EB4-B1E2-4DF0-BAB0-8809D7F5FECF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1568,573 +1569,573 @@
     </row>
     <row r="2" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>16</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>17</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <f>COUNTIF(A1:A100,H4)</f>
+        <f t="shared" ref="I4:I13" si="0">COUNTIF(A1:A100,H4)</f>
         <v>2</v>
       </c>
       <c r="J4">
-        <f>COUNTIF(B1:B100,H4)</f>
+        <f t="shared" ref="J4:J13" si="1">COUNTIF(B1:B100,H4)</f>
         <v>2</v>
       </c>
       <c r="K4">
-        <f>COUNTIF(C1:C100,H4)</f>
+        <f t="shared" ref="K4:K13" si="2">COUNTIF(C1:C100,H4)</f>
         <v>3</v>
       </c>
       <c r="L4">
-        <f>COUNTIF(D1:D100,H4)</f>
+        <f t="shared" ref="L4:L13" si="3">COUNTIF(D1:D100,H4)</f>
         <v>2</v>
       </c>
       <c r="M4">
-        <f>COUNTIF(E1:E100,H4)</f>
+        <f t="shared" ref="M4:M13" si="4">COUNTIF(E1:E100,H4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5">
-        <f>COUNTIF(A2:A101,H5)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="J5">
-        <f t="shared" ref="J5:J13" si="0">COUNTIF(B2:B101,H5)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="K5">
-        <f t="shared" ref="K5:K13" si="1">COUNTIF(C2:C101,H5)</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="L5">
-        <f t="shared" ref="L5:L13" si="2">COUNTIF(D2:D101,H5)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="M5">
-        <f t="shared" ref="M5:M13" si="3">COUNTIF(E2:E101,H5)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I13" si="4">COUNTIF(A3:A102,H6)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="J6">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K6">
+      <c r="J12">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="M6">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12">
+      <c r="M12">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="J12">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K13">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L13">
+      <c r="K13">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="M13">
+      <c r="L13">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
+      <c r="M13">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <f>SUM(I4:I13)</f>
         <v>47</v>
       </c>
       <c r="J14">
-        <f t="shared" ref="J14:M14" si="5">SUM(J4:J13)</f>
+        <f>SUM(J4:J13)</f>
         <v>45</v>
       </c>
       <c r="K14">
-        <f t="shared" si="5"/>
+        <f>SUM(K4:K13)</f>
         <v>37</v>
       </c>
       <c r="L14">
-        <f t="shared" si="5"/>
+        <f>SUM(L4:L13)</f>
         <v>46</v>
       </c>
       <c r="M14">
-        <f t="shared" si="5"/>
+        <f>SUM(M4:M13)</f>
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2142,13 +2143,13 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
         <v>13</v>
@@ -2156,47 +2157,47 @@
     </row>
     <row r="21" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" t="s">
         <v>13</v>
@@ -2207,70 +2208,70 @@
     </row>
     <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2278,372 +2279,1842 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M77"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <f>COUNTIF(A2:A102,H6)</f>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f>COUNTIF(B2:B102,H6)</f>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <f>COUNTIF(C2:C102,H6)</f>
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <f>COUNTIF(D2:D102,H6)</f>
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <f>COUNTIF(E2:E102,H6)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <f>COUNTIF(A2:A103,H7)</f>
+        <v>6</v>
+      </c>
+      <c r="J7">
+        <f>COUNTIF(B2:B103,H7)</f>
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <f>COUNTIF(C2:C103,H7)</f>
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <f>COUNTIF(D2:D103,H7)</f>
+        <v>6</v>
+      </c>
+      <c r="M7">
+        <f>COUNTIF(E2:E103,H7)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <f>COUNTIF(A2:A104,H8)</f>
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <f>COUNTIF(B2:B104,H8)</f>
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <f>COUNTIF(C2:C104,H8)</f>
+        <v>6</v>
+      </c>
+      <c r="L8">
+        <f>COUNTIF(D2:D104,H8)</f>
+        <v>4</v>
+      </c>
+      <c r="M8">
+        <f>COUNTIF(E2:E104,H8)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <f>COUNTIF(A2:A105,H9)</f>
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <f>COUNTIF(B2:B105,H9)</f>
+        <v>5</v>
+      </c>
+      <c r="K9">
+        <f>COUNTIF(C2:C105,H9)</f>
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <f>COUNTIF(D2:D105,H9)</f>
+        <v>7</v>
+      </c>
+      <c r="M9">
+        <f>COUNTIF(E2:E105,H9)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10">
+        <f>COUNTIF(A2:A106,H10)</f>
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <f>COUNTIF(B2:B106,H10)</f>
+        <v>9</v>
+      </c>
+      <c r="K10">
+        <f>COUNTIF(C2:C106,H10)</f>
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <f>COUNTIF(D2:D106,H10)</f>
+        <v>12</v>
+      </c>
+      <c r="M10">
+        <f>COUNTIF(E2:E106,H10)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11">
+        <f>COUNTIF(A2:A107,H11)</f>
+        <v>11</v>
+      </c>
+      <c r="J11">
+        <f>COUNTIF(B2:B107,H11)</f>
+        <v>11</v>
+      </c>
+      <c r="K11">
+        <f>COUNTIF(C2:C107,H11)</f>
+        <v>7</v>
+      </c>
+      <c r="L11">
+        <f>COUNTIF(D2:D107,H11)</f>
+        <v>12</v>
+      </c>
+      <c r="M11">
+        <f>COUNTIF(E2:E107,H11)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <f>COUNTIF(A2:A108,H12)</f>
+        <v>14</v>
+      </c>
+      <c r="J12">
+        <f>COUNTIF(B2:B108,H12)</f>
+        <v>12</v>
+      </c>
+      <c r="K12">
+        <f>COUNTIF(C2:C108,H12)</f>
+        <v>8</v>
+      </c>
+      <c r="L12">
+        <f>COUNTIF(D2:D108,H12)</f>
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <f>COUNTIF(E2:E108,H12)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13">
+        <f>COUNTIF(A2:A109,H13)</f>
+        <v>14</v>
+      </c>
+      <c r="J13">
+        <f>COUNTIF(B2:B109,H13)</f>
+        <v>11</v>
+      </c>
+      <c r="K13">
+        <f>COUNTIF(C2:C109,H13)</f>
+        <v>12</v>
+      </c>
+      <c r="L13">
+        <f>COUNTIF(D2:D109,H13)</f>
+        <v>13</v>
+      </c>
+      <c r="M13">
+        <f>COUNTIF(E2:E109,H13)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14">
+        <f>COUNTIF(A2:A110,H14)</f>
+        <v>5</v>
+      </c>
+      <c r="J14">
+        <f>COUNTIF(B2:B110,H14)</f>
+        <v>6</v>
+      </c>
+      <c r="K14">
+        <f>COUNTIF(C2:C110,H14)</f>
+        <v>4</v>
+      </c>
+      <c r="L14">
+        <f>COUNTIF(D2:D110,H14)</f>
+        <v>6</v>
+      </c>
+      <c r="M14">
+        <f>COUNTIF(E2:E110,H14)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15">
+        <f>COUNTIF(A2:A111,H15)</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f>COUNTIF(B2:B111,H15)</f>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f>COUNTIF(C2:C111,H15)</f>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f>COUNTIF(D2:D111,H15)</f>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" ref="M15" si="0">COUNTIF(E2:E111,L15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <f>SUM(I6:I15)</f>
+        <v>76</v>
+      </c>
+      <c r="J16">
+        <f>SUM(J6:J15)</f>
+        <v>68</v>
+      </c>
+      <c r="K16">
+        <f>SUM(K6:K15)</f>
+        <v>59</v>
+      </c>
+      <c r="L16">
+        <f>SUM(L6:L15)</f>
+        <v>75</v>
+      </c>
+      <c r="M16">
+        <f>SUM(M6:M15)</f>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>13</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>